--- a/accountant-skill/data/output/Sep2025/trial_balance_Sep2025.xlsx
+++ b/accountant-skill/data/output/Sep2025/trial_balance_Sep2025.xlsx
@@ -480,7 +480,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dr: 1,696,964,076.98 | Cr: 1,698,177,775.91</t>
+          <t>Dr: 2,168,513,258.69 | Cr: 2,169,726,957.62</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dr: 1,780,718,170.12 | Cr: 1,781,931,869.05</t>
+          <t>Dr: 2,237,543,394.10 | Cr: 2,238,757,093.03</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1585523.7</v>
+        <v>7190700.700000005</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>6515831.8</v>
@@ -658,7 +658,7 @@
         <v>7190701</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>910654.5</v>
+        <v>6515831.500000004</v>
       </c>
     </row>
     <row r="9">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>4793458.719999998</v>
+        <v>12692758.72</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>15343618.15</v>
@@ -680,7 +680,7 @@
         <v>12692758.27</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>7444318.599999998</v>
+        <v>15343618.6</v>
       </c>
     </row>
     <row r="10">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2016941.289999999</v>
+        <v>32444704.71</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>17720747.46</v>
@@ -702,7 +702,7 @@
         <v>32444705.19</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>16740899.02</v>
+        <v>17720746.98</v>
       </c>
     </row>
     <row r="11">
@@ -779,12 +779,12 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>210290000</v>
+        <v>429290000</v>
       </c>
       <c r="D15" s="4" t="n"/>
       <c r="E15" s="4" t="n"/>
       <c r="F15" s="4" t="n">
-        <v>210290000</v>
+        <v>429290000</v>
       </c>
     </row>
     <row r="16">
@@ -797,12 +797,12 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>316445000</v>
+        <v>449445000</v>
       </c>
       <c r="D16" s="4" t="n"/>
       <c r="E16" s="4" t="n"/>
       <c r="F16" s="4" t="n">
-        <v>316445000</v>
+        <v>449445000</v>
       </c>
     </row>
     <row r="17">
@@ -815,14 +815,14 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>3879167.68</v>
+        <v>23829167.68000001</v>
       </c>
       <c r="D17" s="4" t="n"/>
       <c r="E17" s="4" t="n">
         <v>554167</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>4433334.68</v>
+        <v>24383334.68000001</v>
       </c>
     </row>
     <row r="18">
@@ -835,14 +835,14 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>69520000</v>
+        <v>135920000</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>2054300</v>
       </c>
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n">
-        <v>71574300</v>
+        <v>137974300</v>
       </c>
     </row>
     <row r="19">
@@ -855,14 +855,14 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>9251529.33</v>
+        <v>21626829.33</v>
       </c>
       <c r="D19" s="4" t="n"/>
       <c r="E19" s="4" t="n">
         <v>1543106</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>10794635.33</v>
+        <v>23169935.33</v>
       </c>
     </row>
     <row r="20">
@@ -903,12 +903,12 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>98881000</v>
+        <v>106081000</v>
       </c>
       <c r="D22" s="4" t="n"/>
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="n">
-        <v>98881000</v>
+        <v>106081000</v>
       </c>
     </row>
     <row r="23">
@@ -921,14 +921,14 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2053397.33</v>
+        <v>3763397.33</v>
       </c>
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="n">
         <v>343087</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2396484.33</v>
+        <v>4106484.33</v>
       </c>
     </row>
     <row r="24">
@@ -1071,12 +1071,12 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1000000000</v>
+        <v>1439530823</v>
       </c>
       <c r="D33" s="4" t="n"/>
       <c r="E33" s="4" t="n"/>
       <c r="F33" s="4" t="n">
-        <v>1000000000</v>
+        <v>1439530823</v>
       </c>
     </row>
     <row r="34">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="B65" s="6" t="n"/>
       <c r="C65" s="7" t="n">
-        <v>1698177775.91</v>
+        <v>2169726957.62</v>
       </c>
       <c r="D65" s="7" t="n">
         <v>144253747.87</v>
@@ -1640,7 +1640,7 @@
         <v>144253747.87</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>1781931869.05</v>
+        <v>2238757093.03</v>
       </c>
     </row>
   </sheetData>
